--- a/Experimental/question 1/Phi_calc.xlsx
+++ b/Experimental/question 1/Phi_calc.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tud365-my.sharepoint.com/personal/fmaiorodrigues_tudelft_nl/Documents/Combustion/Assignments/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Documents\GitHub\AE4262-Assignment\Experimental\question 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{B85172A8-837B-44CC-B559-727F8BB139E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21AD5F66-46A1-41DE-B911-AC7888D9F12A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C378681-ADCE-43EE-AD09-50D6A3B99FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{CEFF3C84-A269-430F-B545-0B81AEC1D7B0}"/>
+    <workbookView xWindow="3132" yWindow="2916" windowWidth="17280" windowHeight="8880" activeTab="3" xr2:uid="{CEFF3C84-A269-430F-B545-0B81AEC1D7B0}"/>
   </bookViews>
   <sheets>
     <sheet name="Chemestry CH4" sheetId="1" r:id="rId1"/>
@@ -839,6 +839,138 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -855,138 +987,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="24" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1011,6 +1011,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet3"/>
@@ -1350,23 +1351,23 @@
       <c r="N3" s="2"/>
       <c r="O3" s="3"/>
       <c r="Q3" s="1"/>
-      <c r="R3" s="99" t="s">
+      <c r="R3" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="99"/>
-      <c r="T3" s="99"/>
-      <c r="U3" s="99"/>
-      <c r="V3" s="99"/>
-      <c r="W3" s="99"/>
-      <c r="X3" s="99"/>
-      <c r="Y3" s="99"/>
-      <c r="Z3" s="99"/>
-      <c r="AA3" s="99"/>
-      <c r="AB3" s="99"/>
-      <c r="AC3" s="99"/>
-      <c r="AD3" s="99"/>
-      <c r="AE3" s="99"/>
-      <c r="AF3" s="100"/>
+      <c r="S3" s="93"/>
+      <c r="T3" s="93"/>
+      <c r="U3" s="93"/>
+      <c r="V3" s="93"/>
+      <c r="W3" s="93"/>
+      <c r="X3" s="93"/>
+      <c r="Y3" s="93"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
+      <c r="AB3" s="93"/>
+      <c r="AC3" s="93"/>
+      <c r="AD3" s="93"/>
+      <c r="AE3" s="93"/>
+      <c r="AF3" s="94"/>
     </row>
     <row r="4" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4"/>
@@ -1384,72 +1385,72 @@
       <c r="AF4" s="5"/>
     </row>
     <row r="5" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="101" t="s">
+      <c r="B5" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="103"/>
-      <c r="H5" s="94" t="s">
+      <c r="C5" s="96"/>
+      <c r="D5" s="96"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="97"/>
+      <c r="H5" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="95"/>
-      <c r="J5" s="96"/>
-      <c r="L5" s="104" t="s">
+      <c r="I5" s="99"/>
+      <c r="J5" s="100"/>
+      <c r="L5" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="M5" s="105"/>
-      <c r="N5" s="106"/>
+      <c r="M5" s="102"/>
+      <c r="N5" s="103"/>
       <c r="O5" s="5"/>
       <c r="P5" s="6" t="s">
         <v>2</v>
       </c>
       <c r="Q5" s="4"/>
-      <c r="R5" s="107" t="s">
+      <c r="R5" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="S5" s="108"/>
-      <c r="T5" s="108"/>
-      <c r="U5" s="108"/>
-      <c r="V5" s="109"/>
-      <c r="X5" s="94" t="s">
+      <c r="S5" s="105"/>
+      <c r="T5" s="105"/>
+      <c r="U5" s="105"/>
+      <c r="V5" s="106"/>
+      <c r="X5" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="Y5" s="95"/>
-      <c r="Z5" s="96"/>
-      <c r="AB5" s="110" t="s">
+      <c r="Y5" s="99"/>
+      <c r="Z5" s="100"/>
+      <c r="AB5" s="107" t="s">
         <v>6</v>
       </c>
-      <c r="AC5" s="111"/>
-      <c r="AD5" s="111"/>
-      <c r="AE5" s="111"/>
-      <c r="AF5" s="112"/>
+      <c r="AC5" s="108"/>
+      <c r="AD5" s="108"/>
+      <c r="AE5" s="108"/>
+      <c r="AF5" s="109"/>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="84" t="s">
+      <c r="C6" s="110" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85"/>
-      <c r="F6" s="86"/>
+      <c r="D6" s="111"/>
+      <c r="E6" s="111"/>
+      <c r="F6" s="112"/>
       <c r="H6" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="97" t="s">
+      <c r="I6" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="98"/>
+      <c r="J6" s="114"/>
       <c r="L6" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="M6" s="87" t="s">
+      <c r="M6" s="115" t="s">
         <v>10</v>
       </c>
-      <c r="N6" s="88"/>
+      <c r="N6" s="116"/>
       <c r="O6" s="5"/>
       <c r="P6" s="6" t="s">
         <v>2</v>
@@ -1458,28 +1459,28 @@
       <c r="R6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="S6" s="89" t="s">
+      <c r="S6" s="117" t="s">
         <v>11</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
-      <c r="V6" s="91"/>
+      <c r="T6" s="118"/>
+      <c r="U6" s="118"/>
+      <c r="V6" s="119"/>
       <c r="X6" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="Y6" s="97" t="s">
+      <c r="Y6" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="Z6" s="98"/>
+      <c r="Z6" s="114"/>
       <c r="AB6" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="AC6" s="92" t="s">
+      <c r="AC6" s="91" t="s">
         <v>11</v>
       </c>
-      <c r="AD6" s="92"/>
-      <c r="AE6" s="92"/>
-      <c r="AF6" s="93"/>
+      <c r="AD6" s="91"/>
+      <c r="AE6" s="91"/>
+      <c r="AF6" s="92"/>
     </row>
     <row r="7" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="10">
@@ -1627,187 +1628,187 @@
         <v>17</v>
       </c>
       <c r="B10" s="41"/>
-      <c r="C10" s="113">
+      <c r="C10" s="88">
         <v>-74.849999999999994</v>
       </c>
-      <c r="D10" s="114"/>
-      <c r="E10" s="114"/>
-      <c r="F10" s="115"/>
+      <c r="D10" s="89"/>
+      <c r="E10" s="89"/>
+      <c r="F10" s="90"/>
       <c r="G10" s="41"/>
       <c r="H10" s="41"/>
-      <c r="I10" s="113">
+      <c r="I10" s="88">
         <v>0</v>
       </c>
-      <c r="J10" s="115"/>
+      <c r="J10" s="90"/>
       <c r="K10" s="41"/>
       <c r="L10" s="41"/>
-      <c r="M10" s="113">
+      <c r="M10" s="88">
         <v>0</v>
       </c>
-      <c r="N10" s="115"/>
+      <c r="N10" s="90"/>
       <c r="O10" s="41"/>
       <c r="P10" s="41" t="s">
         <v>2</v>
       </c>
       <c r="Q10" s="41"/>
       <c r="R10" s="41"/>
-      <c r="S10" s="113">
+      <c r="S10" s="88">
         <v>-393</v>
       </c>
-      <c r="T10" s="114"/>
-      <c r="U10" s="114"/>
-      <c r="V10" s="115"/>
+      <c r="T10" s="89"/>
+      <c r="U10" s="89"/>
+      <c r="V10" s="90"/>
       <c r="W10" s="41"/>
       <c r="X10" s="41"/>
-      <c r="Y10" s="113">
+      <c r="Y10" s="88">
         <v>0</v>
       </c>
-      <c r="Z10" s="115"/>
+      <c r="Z10" s="90"/>
       <c r="AA10" s="41"/>
       <c r="AB10" s="41"/>
-      <c r="AC10" s="113">
+      <c r="AC10" s="88">
         <v>-241.81</v>
       </c>
-      <c r="AD10" s="114"/>
-      <c r="AE10" s="114"/>
-      <c r="AF10" s="115"/>
+      <c r="AD10" s="89"/>
+      <c r="AE10" s="89"/>
+      <c r="AF10" s="90"/>
     </row>
     <row r="11" spans="1:32" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="40" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="41"/>
-      <c r="C11" s="116">
+      <c r="C11" s="85">
         <f>C10*B7</f>
         <v>-74.849999999999994</v>
       </c>
-      <c r="D11" s="117"/>
-      <c r="E11" s="117"/>
-      <c r="F11" s="118"/>
+      <c r="D11" s="86"/>
+      <c r="E11" s="86"/>
+      <c r="F11" s="87"/>
       <c r="G11" s="41"/>
       <c r="H11" s="41"/>
-      <c r="I11" s="116">
+      <c r="I11" s="85">
         <v>0</v>
       </c>
-      <c r="J11" s="118"/>
+      <c r="J11" s="87"/>
       <c r="K11" s="41"/>
       <c r="L11" s="41"/>
-      <c r="M11" s="116">
+      <c r="M11" s="85">
         <f>L7*M10</f>
         <v>0</v>
       </c>
-      <c r="N11" s="118"/>
+      <c r="N11" s="87"/>
       <c r="O11" s="41"/>
       <c r="P11" s="41" t="s">
         <v>2</v>
       </c>
       <c r="Q11" s="41"/>
       <c r="R11" s="41"/>
-      <c r="S11" s="116">
+      <c r="S11" s="85">
         <f>S10*R7</f>
         <v>-393</v>
       </c>
-      <c r="T11" s="117"/>
-      <c r="U11" s="117"/>
-      <c r="V11" s="118"/>
+      <c r="T11" s="86"/>
+      <c r="U11" s="86"/>
+      <c r="V11" s="87"/>
       <c r="W11" s="42"/>
       <c r="X11" s="42"/>
-      <c r="Y11" s="116">
+      <c r="Y11" s="85">
         <v>0</v>
       </c>
-      <c r="Z11" s="118"/>
+      <c r="Z11" s="87"/>
       <c r="AA11" s="42"/>
       <c r="AB11" s="42"/>
-      <c r="AC11" s="116">
+      <c r="AC11" s="85">
         <f>AC10*AB7</f>
         <v>-483.62</v>
       </c>
-      <c r="AD11" s="117"/>
-      <c r="AE11" s="117"/>
-      <c r="AF11" s="118"/>
+      <c r="AD11" s="86"/>
+      <c r="AE11" s="86"/>
+      <c r="AF11" s="87"/>
     </row>
     <row r="12" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="13" spans="1:32" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="120">
+      <c r="B13" s="79">
         <f>C11+M11</f>
         <v>-74.849999999999994</v>
       </c>
-      <c r="C13" s="121"/>
-      <c r="D13" s="121"/>
-      <c r="E13" s="121"/>
-      <c r="F13" s="121"/>
-      <c r="G13" s="121"/>
-      <c r="H13" s="121"/>
-      <c r="I13" s="121"/>
-      <c r="J13" s="121"/>
-      <c r="K13" s="121"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="122"/>
+      <c r="C13" s="80"/>
+      <c r="D13" s="80"/>
+      <c r="E13" s="80"/>
+      <c r="F13" s="80"/>
+      <c r="G13" s="80"/>
+      <c r="H13" s="80"/>
+      <c r="I13" s="80"/>
+      <c r="J13" s="80"/>
+      <c r="K13" s="80"/>
+      <c r="L13" s="80"/>
+      <c r="M13" s="80"/>
+      <c r="N13" s="80"/>
+      <c r="O13" s="81"/>
       <c r="P13" s="41"/>
-      <c r="Q13" s="120">
+      <c r="Q13" s="79">
         <f>S11+AC11</f>
         <v>-876.62</v>
       </c>
-      <c r="R13" s="121"/>
-      <c r="S13" s="121"/>
-      <c r="T13" s="121"/>
-      <c r="U13" s="121"/>
-      <c r="V13" s="121"/>
-      <c r="W13" s="121"/>
-      <c r="X13" s="121"/>
-      <c r="Y13" s="121"/>
-      <c r="Z13" s="121"/>
-      <c r="AA13" s="121"/>
-      <c r="AB13" s="121"/>
-      <c r="AC13" s="121"/>
-      <c r="AD13" s="121"/>
-      <c r="AE13" s="121"/>
-      <c r="AF13" s="122"/>
+      <c r="R13" s="80"/>
+      <c r="S13" s="80"/>
+      <c r="T13" s="80"/>
+      <c r="U13" s="80"/>
+      <c r="V13" s="80"/>
+      <c r="W13" s="80"/>
+      <c r="X13" s="80"/>
+      <c r="Y13" s="80"/>
+      <c r="Z13" s="80"/>
+      <c r="AA13" s="80"/>
+      <c r="AB13" s="80"/>
+      <c r="AC13" s="80"/>
+      <c r="AD13" s="80"/>
+      <c r="AE13" s="80"/>
+      <c r="AF13" s="81"/>
     </row>
     <row r="14" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="15" spans="1:32" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="120">
+      <c r="B15" s="79">
         <f>Q13-B13</f>
         <v>-801.77</v>
       </c>
-      <c r="C15" s="121"/>
-      <c r="D15" s="121"/>
-      <c r="E15" s="121"/>
-      <c r="F15" s="121"/>
-      <c r="G15" s="121"/>
-      <c r="H15" s="121"/>
-      <c r="I15" s="121"/>
-      <c r="J15" s="121"/>
-      <c r="K15" s="121"/>
-      <c r="L15" s="121"/>
-      <c r="M15" s="121"/>
-      <c r="N15" s="121"/>
-      <c r="O15" s="121"/>
-      <c r="P15" s="121"/>
-      <c r="Q15" s="121"/>
-      <c r="R15" s="121"/>
-      <c r="S15" s="121"/>
-      <c r="T15" s="121"/>
-      <c r="U15" s="121"/>
-      <c r="V15" s="121"/>
-      <c r="W15" s="121"/>
-      <c r="X15" s="121"/>
-      <c r="Y15" s="121"/>
-      <c r="Z15" s="121"/>
-      <c r="AA15" s="121"/>
-      <c r="AB15" s="121"/>
-      <c r="AC15" s="121"/>
-      <c r="AD15" s="121"/>
-      <c r="AE15" s="121"/>
-      <c r="AF15" s="122"/>
+      <c r="C15" s="80"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="80"/>
+      <c r="H15" s="80"/>
+      <c r="I15" s="80"/>
+      <c r="J15" s="80"/>
+      <c r="K15" s="80"/>
+      <c r="L15" s="80"/>
+      <c r="M15" s="80"/>
+      <c r="N15" s="80"/>
+      <c r="O15" s="80"/>
+      <c r="P15" s="80"/>
+      <c r="Q15" s="80"/>
+      <c r="R15" s="80"/>
+      <c r="S15" s="80"/>
+      <c r="T15" s="80"/>
+      <c r="U15" s="80"/>
+      <c r="V15" s="80"/>
+      <c r="W15" s="80"/>
+      <c r="X15" s="80"/>
+      <c r="Y15" s="80"/>
+      <c r="Z15" s="80"/>
+      <c r="AA15" s="80"/>
+      <c r="AB15" s="80"/>
+      <c r="AC15" s="80"/>
+      <c r="AD15" s="80"/>
+      <c r="AE15" s="80"/>
+      <c r="AF15" s="81"/>
     </row>
     <row r="17" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1815,27 +1816,27 @@
         <v>21</v>
       </c>
       <c r="B18" s="26"/>
-      <c r="C18" s="123">
+      <c r="C18" s="82">
         <f>D7*C21+F7*F21</f>
         <v>16.032</v>
       </c>
-      <c r="D18" s="124"/>
-      <c r="E18" s="124"/>
-      <c r="F18" s="125"/>
+      <c r="D18" s="83"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="84"/>
       <c r="G18" s="26"/>
       <c r="H18" s="26"/>
-      <c r="I18" s="123">
+      <c r="I18" s="82">
         <f>J7*J21</f>
         <v>28</v>
       </c>
-      <c r="J18" s="125"/>
+      <c r="J18" s="84"/>
       <c r="K18" s="26"/>
       <c r="L18" s="26"/>
-      <c r="M18" s="123">
+      <c r="M18" s="82">
         <f>N7*M21</f>
         <v>32</v>
       </c>
-      <c r="N18" s="125"/>
+      <c r="N18" s="84"/>
       <c r="O18" s="27" t="s">
         <v>22</v>
       </c>
@@ -1844,56 +1845,56 @@
         <v>22</v>
       </c>
       <c r="R18" s="26"/>
-      <c r="S18" s="123">
+      <c r="S18" s="82">
         <f>T7*C21+V7*M21</f>
         <v>44</v>
       </c>
-      <c r="T18" s="124"/>
-      <c r="U18" s="124"/>
-      <c r="V18" s="125"/>
+      <c r="T18" s="83"/>
+      <c r="U18" s="83"/>
+      <c r="V18" s="84"/>
       <c r="W18" s="26"/>
       <c r="X18" s="26"/>
-      <c r="Y18" s="123">
+      <c r="Y18" s="82">
         <f>J21*Z7</f>
         <v>28</v>
       </c>
-      <c r="Z18" s="125"/>
+      <c r="Z18" s="84"/>
       <c r="AA18" s="26"/>
       <c r="AB18" s="26"/>
-      <c r="AC18" s="123">
+      <c r="AC18" s="82">
         <f>AD7*F21+AF7*M21</f>
         <v>18.015999999999998</v>
       </c>
-      <c r="AD18" s="124"/>
-      <c r="AE18" s="124"/>
-      <c r="AF18" s="125"/>
+      <c r="AD18" s="83"/>
+      <c r="AE18" s="83"/>
+      <c r="AF18" s="84"/>
     </row>
     <row r="19" spans="1:32" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="28" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="26"/>
-      <c r="C19" s="82">
+      <c r="C19" s="76">
         <f>C18*B7</f>
         <v>16.032</v>
       </c>
-      <c r="D19" s="119"/>
-      <c r="E19" s="119"/>
-      <c r="F19" s="83"/>
+      <c r="D19" s="77"/>
+      <c r="E19" s="77"/>
+      <c r="F19" s="78"/>
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
-      <c r="I19" s="82">
+      <c r="I19" s="76">
         <f>I18*H7</f>
         <v>208.32000000000002</v>
       </c>
-      <c r="J19" s="83"/>
+      <c r="J19" s="78"/>
       <c r="K19" s="26"/>
       <c r="L19" s="26"/>
-      <c r="M19" s="82">
+      <c r="M19" s="76">
         <f>M18*L7</f>
         <v>64</v>
       </c>
-      <c r="N19" s="83"/>
+      <c r="N19" s="78"/>
       <c r="O19" s="29">
         <f>M19+C19+I19</f>
         <v>288.35200000000003</v>
@@ -1904,35 +1905,35 @@
         <v>288.35200000000003</v>
       </c>
       <c r="R19" s="26"/>
-      <c r="S19" s="82">
+      <c r="S19" s="76">
         <f>S18*R7</f>
         <v>44</v>
       </c>
-      <c r="T19" s="119"/>
-      <c r="U19" s="119">
+      <c r="T19" s="77"/>
+      <c r="U19" s="77">
         <f t="shared" ref="U19" si="0">U18*T7</f>
         <v>0</v>
       </c>
-      <c r="V19" s="83"/>
+      <c r="V19" s="78"/>
       <c r="W19" s="26"/>
       <c r="X19" s="26"/>
-      <c r="Y19" s="82">
+      <c r="Y19" s="76">
         <f>Y18*X7</f>
         <v>208.32000000000002</v>
       </c>
-      <c r="Z19" s="83"/>
+      <c r="Z19" s="78"/>
       <c r="AA19" s="26"/>
       <c r="AB19" s="26"/>
-      <c r="AC19" s="82">
+      <c r="AC19" s="76">
         <f>AC18*AB7</f>
         <v>36.031999999999996</v>
       </c>
-      <c r="AD19" s="119"/>
-      <c r="AE19" s="119">
+      <c r="AD19" s="77"/>
+      <c r="AE19" s="77">
         <f t="shared" ref="AE19" si="1">AE18*AD7</f>
         <v>0</v>
       </c>
-      <c r="AF19" s="83"/>
+      <c r="AF19" s="78"/>
     </row>
     <row r="20" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="21" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2041,6 +2042,7 @@
     <mergeCell ref="S18:V18"/>
     <mergeCell ref="AC18:AF18"/>
     <mergeCell ref="I18:J18"/>
+    <mergeCell ref="B13:O13"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="L5:N5"/>
     <mergeCell ref="R5:V5"/>
@@ -2071,7 +2073,6 @@
     <mergeCell ref="M19:N19"/>
     <mergeCell ref="S19:V19"/>
     <mergeCell ref="AC19:AF19"/>
-    <mergeCell ref="B13:O13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="42" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -2108,23 +2109,23 @@
       <c r="N3" s="2"/>
       <c r="O3" s="3"/>
       <c r="Q3" s="1"/>
-      <c r="R3" s="99" t="s">
+      <c r="R3" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="99"/>
-      <c r="T3" s="99"/>
-      <c r="U3" s="99"/>
-      <c r="V3" s="99"/>
-      <c r="W3" s="99"/>
-      <c r="X3" s="99"/>
-      <c r="Y3" s="99"/>
-      <c r="Z3" s="99"/>
-      <c r="AA3" s="99"/>
-      <c r="AB3" s="99"/>
-      <c r="AC3" s="99"/>
-      <c r="AD3" s="99"/>
-      <c r="AE3" s="99"/>
-      <c r="AF3" s="100"/>
+      <c r="S3" s="93"/>
+      <c r="T3" s="93"/>
+      <c r="U3" s="93"/>
+      <c r="V3" s="93"/>
+      <c r="W3" s="93"/>
+      <c r="X3" s="93"/>
+      <c r="Y3" s="93"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
+      <c r="AB3" s="93"/>
+      <c r="AC3" s="93"/>
+      <c r="AD3" s="93"/>
+      <c r="AE3" s="93"/>
+      <c r="AF3" s="94"/>
     </row>
     <row r="4" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4"/>
@@ -2142,72 +2143,72 @@
       <c r="AF4" s="5"/>
     </row>
     <row r="5" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="101" t="s">
+      <c r="B5" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="103"/>
-      <c r="H5" s="94" t="s">
+      <c r="C5" s="96"/>
+      <c r="D5" s="96"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="97"/>
+      <c r="H5" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="95"/>
-      <c r="J5" s="96"/>
-      <c r="L5" s="104" t="s">
+      <c r="I5" s="99"/>
+      <c r="J5" s="100"/>
+      <c r="L5" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="M5" s="105"/>
-      <c r="N5" s="106"/>
+      <c r="M5" s="102"/>
+      <c r="N5" s="103"/>
       <c r="O5" s="5"/>
       <c r="P5" s="6" t="s">
         <v>2</v>
       </c>
       <c r="Q5" s="4"/>
-      <c r="R5" s="107" t="s">
+      <c r="R5" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="S5" s="108"/>
-      <c r="T5" s="108"/>
-      <c r="U5" s="108"/>
-      <c r="V5" s="109"/>
-      <c r="X5" s="94" t="s">
+      <c r="S5" s="105"/>
+      <c r="T5" s="105"/>
+      <c r="U5" s="105"/>
+      <c r="V5" s="106"/>
+      <c r="X5" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="Y5" s="95"/>
-      <c r="Z5" s="96"/>
-      <c r="AB5" s="110" t="s">
+      <c r="Y5" s="99"/>
+      <c r="Z5" s="100"/>
+      <c r="AB5" s="107" t="s">
         <v>6</v>
       </c>
-      <c r="AC5" s="111"/>
-      <c r="AD5" s="111"/>
-      <c r="AE5" s="111"/>
-      <c r="AF5" s="112"/>
+      <c r="AC5" s="108"/>
+      <c r="AD5" s="108"/>
+      <c r="AE5" s="108"/>
+      <c r="AF5" s="109"/>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="84" t="s">
+      <c r="C6" s="110" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85"/>
-      <c r="F6" s="86"/>
+      <c r="D6" s="111"/>
+      <c r="E6" s="111"/>
+      <c r="F6" s="112"/>
       <c r="H6" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="97" t="s">
+      <c r="I6" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="98"/>
+      <c r="J6" s="114"/>
       <c r="L6" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="M6" s="87" t="s">
+      <c r="M6" s="115" t="s">
         <v>10</v>
       </c>
-      <c r="N6" s="88"/>
+      <c r="N6" s="116"/>
       <c r="O6" s="5"/>
       <c r="P6" s="6" t="s">
         <v>2</v>
@@ -2216,28 +2217,28 @@
       <c r="R6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="S6" s="89" t="s">
+      <c r="S6" s="117" t="s">
         <v>11</v>
       </c>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
-      <c r="V6" s="91"/>
+      <c r="T6" s="118"/>
+      <c r="U6" s="118"/>
+      <c r="V6" s="119"/>
       <c r="X6" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="Y6" s="97" t="s">
+      <c r="Y6" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="Z6" s="98"/>
+      <c r="Z6" s="114"/>
       <c r="AB6" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="AC6" s="92" t="s">
+      <c r="AC6" s="91" t="s">
         <v>11</v>
       </c>
-      <c r="AD6" s="92"/>
-      <c r="AE6" s="92"/>
-      <c r="AF6" s="93"/>
+      <c r="AD6" s="91"/>
+      <c r="AE6" s="91"/>
+      <c r="AF6" s="92"/>
     </row>
     <row r="7" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="10">
@@ -2385,187 +2386,187 @@
         <v>17</v>
       </c>
       <c r="B10" s="41"/>
-      <c r="C10" s="113">
+      <c r="C10" s="88">
         <v>0</v>
       </c>
-      <c r="D10" s="114"/>
-      <c r="E10" s="114"/>
-      <c r="F10" s="115"/>
+      <c r="D10" s="89"/>
+      <c r="E10" s="89"/>
+      <c r="F10" s="90"/>
       <c r="G10" s="41"/>
       <c r="H10" s="41"/>
-      <c r="I10" s="113">
+      <c r="I10" s="88">
         <v>0</v>
       </c>
-      <c r="J10" s="115"/>
+      <c r="J10" s="90"/>
       <c r="K10" s="41"/>
       <c r="L10" s="41"/>
-      <c r="M10" s="113">
+      <c r="M10" s="88">
         <v>0</v>
       </c>
-      <c r="N10" s="115"/>
+      <c r="N10" s="90"/>
       <c r="O10" s="41"/>
       <c r="P10" s="41" t="s">
         <v>2</v>
       </c>
       <c r="Q10" s="41"/>
       <c r="R10" s="41"/>
-      <c r="S10" s="113">
+      <c r="S10" s="88">
         <v>-393</v>
       </c>
-      <c r="T10" s="114"/>
-      <c r="U10" s="114"/>
-      <c r="V10" s="115"/>
+      <c r="T10" s="89"/>
+      <c r="U10" s="89"/>
+      <c r="V10" s="90"/>
       <c r="W10" s="41"/>
       <c r="X10" s="41"/>
-      <c r="Y10" s="113">
+      <c r="Y10" s="88">
         <v>0</v>
       </c>
-      <c r="Z10" s="115"/>
+      <c r="Z10" s="90"/>
       <c r="AA10" s="41"/>
       <c r="AB10" s="41"/>
-      <c r="AC10" s="113">
+      <c r="AC10" s="88">
         <v>-241.81</v>
       </c>
-      <c r="AD10" s="114"/>
-      <c r="AE10" s="114"/>
-      <c r="AF10" s="115"/>
+      <c r="AD10" s="89"/>
+      <c r="AE10" s="89"/>
+      <c r="AF10" s="90"/>
     </row>
     <row r="11" spans="1:32" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="40" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="41"/>
-      <c r="C11" s="116">
+      <c r="C11" s="85">
         <f>C10*B7</f>
         <v>0</v>
       </c>
-      <c r="D11" s="117"/>
-      <c r="E11" s="117"/>
-      <c r="F11" s="118"/>
+      <c r="D11" s="86"/>
+      <c r="E11" s="86"/>
+      <c r="F11" s="87"/>
       <c r="G11" s="41"/>
       <c r="H11" s="41"/>
-      <c r="I11" s="116">
+      <c r="I11" s="85">
         <v>0</v>
       </c>
-      <c r="J11" s="118"/>
+      <c r="J11" s="87"/>
       <c r="K11" s="41"/>
       <c r="L11" s="41"/>
-      <c r="M11" s="116">
+      <c r="M11" s="85">
         <f>L7*M10</f>
         <v>0</v>
       </c>
-      <c r="N11" s="118"/>
+      <c r="N11" s="87"/>
       <c r="O11" s="41"/>
       <c r="P11" s="41" t="s">
         <v>2</v>
       </c>
       <c r="Q11" s="41"/>
       <c r="R11" s="41"/>
-      <c r="S11" s="116">
+      <c r="S11" s="85">
         <f>S10*R7</f>
         <v>0</v>
       </c>
-      <c r="T11" s="117"/>
-      <c r="U11" s="117"/>
-      <c r="V11" s="118"/>
+      <c r="T11" s="86"/>
+      <c r="U11" s="86"/>
+      <c r="V11" s="87"/>
       <c r="W11" s="42"/>
       <c r="X11" s="42"/>
-      <c r="Y11" s="116">
+      <c r="Y11" s="85">
         <v>0</v>
       </c>
-      <c r="Z11" s="118"/>
+      <c r="Z11" s="87"/>
       <c r="AA11" s="42"/>
       <c r="AB11" s="42"/>
-      <c r="AC11" s="116">
+      <c r="AC11" s="85">
         <f>AC10*AB7</f>
         <v>-241.81</v>
       </c>
-      <c r="AD11" s="117"/>
-      <c r="AE11" s="117"/>
-      <c r="AF11" s="118"/>
+      <c r="AD11" s="86"/>
+      <c r="AE11" s="86"/>
+      <c r="AF11" s="87"/>
     </row>
     <row r="12" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="13" spans="1:32" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="120">
+      <c r="B13" s="79">
         <f>C11+M11</f>
         <v>0</v>
       </c>
-      <c r="C13" s="121"/>
-      <c r="D13" s="121"/>
-      <c r="E13" s="121"/>
-      <c r="F13" s="121"/>
-      <c r="G13" s="121"/>
-      <c r="H13" s="121"/>
-      <c r="I13" s="121"/>
-      <c r="J13" s="121"/>
-      <c r="K13" s="121"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="122"/>
+      <c r="C13" s="80"/>
+      <c r="D13" s="80"/>
+      <c r="E13" s="80"/>
+      <c r="F13" s="80"/>
+      <c r="G13" s="80"/>
+      <c r="H13" s="80"/>
+      <c r="I13" s="80"/>
+      <c r="J13" s="80"/>
+      <c r="K13" s="80"/>
+      <c r="L13" s="80"/>
+      <c r="M13" s="80"/>
+      <c r="N13" s="80"/>
+      <c r="O13" s="81"/>
       <c r="P13" s="41"/>
-      <c r="Q13" s="120">
+      <c r="Q13" s="79">
         <f>S11+AC11</f>
         <v>-241.81</v>
       </c>
-      <c r="R13" s="121"/>
-      <c r="S13" s="121"/>
-      <c r="T13" s="121"/>
-      <c r="U13" s="121"/>
-      <c r="V13" s="121"/>
-      <c r="W13" s="121"/>
-      <c r="X13" s="121"/>
-      <c r="Y13" s="121"/>
-      <c r="Z13" s="121"/>
-      <c r="AA13" s="121"/>
-      <c r="AB13" s="121"/>
-      <c r="AC13" s="121"/>
-      <c r="AD13" s="121"/>
-      <c r="AE13" s="121"/>
-      <c r="AF13" s="122"/>
+      <c r="R13" s="80"/>
+      <c r="S13" s="80"/>
+      <c r="T13" s="80"/>
+      <c r="U13" s="80"/>
+      <c r="V13" s="80"/>
+      <c r="W13" s="80"/>
+      <c r="X13" s="80"/>
+      <c r="Y13" s="80"/>
+      <c r="Z13" s="80"/>
+      <c r="AA13" s="80"/>
+      <c r="AB13" s="80"/>
+      <c r="AC13" s="80"/>
+      <c r="AD13" s="80"/>
+      <c r="AE13" s="80"/>
+      <c r="AF13" s="81"/>
     </row>
     <row r="14" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="15" spans="1:32" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="120">
+      <c r="B15" s="79">
         <f>Q13-B13</f>
         <v>-241.81</v>
       </c>
-      <c r="C15" s="121"/>
-      <c r="D15" s="121"/>
-      <c r="E15" s="121"/>
-      <c r="F15" s="121"/>
-      <c r="G15" s="121"/>
-      <c r="H15" s="121"/>
-      <c r="I15" s="121"/>
-      <c r="J15" s="121"/>
-      <c r="K15" s="121"/>
-      <c r="L15" s="121"/>
-      <c r="M15" s="121"/>
-      <c r="N15" s="121"/>
-      <c r="O15" s="121"/>
-      <c r="P15" s="121"/>
-      <c r="Q15" s="121"/>
-      <c r="R15" s="121"/>
-      <c r="S15" s="121"/>
-      <c r="T15" s="121"/>
-      <c r="U15" s="121"/>
-      <c r="V15" s="121"/>
-      <c r="W15" s="121"/>
-      <c r="X15" s="121"/>
-      <c r="Y15" s="121"/>
-      <c r="Z15" s="121"/>
-      <c r="AA15" s="121"/>
-      <c r="AB15" s="121"/>
-      <c r="AC15" s="121"/>
-      <c r="AD15" s="121"/>
-      <c r="AE15" s="121"/>
-      <c r="AF15" s="122"/>
+      <c r="C15" s="80"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="80"/>
+      <c r="H15" s="80"/>
+      <c r="I15" s="80"/>
+      <c r="J15" s="80"/>
+      <c r="K15" s="80"/>
+      <c r="L15" s="80"/>
+      <c r="M15" s="80"/>
+      <c r="N15" s="80"/>
+      <c r="O15" s="80"/>
+      <c r="P15" s="80"/>
+      <c r="Q15" s="80"/>
+      <c r="R15" s="80"/>
+      <c r="S15" s="80"/>
+      <c r="T15" s="80"/>
+      <c r="U15" s="80"/>
+      <c r="V15" s="80"/>
+      <c r="W15" s="80"/>
+      <c r="X15" s="80"/>
+      <c r="Y15" s="80"/>
+      <c r="Z15" s="80"/>
+      <c r="AA15" s="80"/>
+      <c r="AB15" s="80"/>
+      <c r="AC15" s="80"/>
+      <c r="AD15" s="80"/>
+      <c r="AE15" s="80"/>
+      <c r="AF15" s="81"/>
     </row>
     <row r="17" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2573,27 +2574,27 @@
         <v>21</v>
       </c>
       <c r="B18" s="26"/>
-      <c r="C18" s="123">
+      <c r="C18" s="82">
         <f>D7*C21+F7*F21</f>
         <v>2.016</v>
       </c>
-      <c r="D18" s="124"/>
-      <c r="E18" s="124"/>
-      <c r="F18" s="125"/>
+      <c r="D18" s="83"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="84"/>
       <c r="G18" s="26"/>
       <c r="H18" s="26"/>
-      <c r="I18" s="123">
+      <c r="I18" s="82">
         <f>J7*J21</f>
         <v>28</v>
       </c>
-      <c r="J18" s="125"/>
+      <c r="J18" s="84"/>
       <c r="K18" s="26"/>
       <c r="L18" s="26"/>
-      <c r="M18" s="123">
+      <c r="M18" s="82">
         <f>N7*M21</f>
         <v>32</v>
       </c>
-      <c r="N18" s="125"/>
+      <c r="N18" s="84"/>
       <c r="O18" s="27" t="s">
         <v>22</v>
       </c>
@@ -2602,56 +2603,56 @@
         <v>22</v>
       </c>
       <c r="R18" s="26"/>
-      <c r="S18" s="123">
+      <c r="S18" s="82">
         <f>T7*C21+V7*M21</f>
         <v>44</v>
       </c>
-      <c r="T18" s="124"/>
-      <c r="U18" s="124"/>
-      <c r="V18" s="125"/>
+      <c r="T18" s="83"/>
+      <c r="U18" s="83"/>
+      <c r="V18" s="84"/>
       <c r="W18" s="26"/>
       <c r="X18" s="26"/>
-      <c r="Y18" s="123">
+      <c r="Y18" s="82">
         <f>J21*Z7</f>
         <v>28</v>
       </c>
-      <c r="Z18" s="125"/>
+      <c r="Z18" s="84"/>
       <c r="AA18" s="26"/>
       <c r="AB18" s="26"/>
-      <c r="AC18" s="123">
+      <c r="AC18" s="82">
         <f>AD7*F21+AF7*M21</f>
         <v>18.015999999999998</v>
       </c>
-      <c r="AD18" s="124"/>
-      <c r="AE18" s="124"/>
-      <c r="AF18" s="125"/>
+      <c r="AD18" s="83"/>
+      <c r="AE18" s="83"/>
+      <c r="AF18" s="84"/>
     </row>
     <row r="19" spans="1:32" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="28" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="26"/>
-      <c r="C19" s="82">
+      <c r="C19" s="76">
         <f>C18*B7</f>
         <v>2.016</v>
       </c>
-      <c r="D19" s="119"/>
-      <c r="E19" s="119"/>
-      <c r="F19" s="83"/>
+      <c r="D19" s="77"/>
+      <c r="E19" s="77"/>
+      <c r="F19" s="78"/>
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
-      <c r="I19" s="82">
+      <c r="I19" s="76">
         <f>I18*H7</f>
         <v>52.080000000000005</v>
       </c>
-      <c r="J19" s="83"/>
+      <c r="J19" s="78"/>
       <c r="K19" s="26"/>
       <c r="L19" s="26"/>
-      <c r="M19" s="82">
+      <c r="M19" s="76">
         <f>M18*L7</f>
         <v>16</v>
       </c>
-      <c r="N19" s="83"/>
+      <c r="N19" s="78"/>
       <c r="O19" s="29">
         <f>M19+C19+I19</f>
         <v>70.096000000000004</v>
@@ -2662,35 +2663,35 @@
         <v>70.096000000000004</v>
       </c>
       <c r="R19" s="26"/>
-      <c r="S19" s="82">
+      <c r="S19" s="76">
         <f>S18*R7</f>
         <v>0</v>
       </c>
-      <c r="T19" s="119"/>
-      <c r="U19" s="119">
+      <c r="T19" s="77"/>
+      <c r="U19" s="77">
         <f t="shared" ref="U19" si="0">U18*T7</f>
         <v>0</v>
       </c>
-      <c r="V19" s="83"/>
+      <c r="V19" s="78"/>
       <c r="W19" s="26"/>
       <c r="X19" s="26"/>
-      <c r="Y19" s="82">
+      <c r="Y19" s="76">
         <f>Y18*X7</f>
         <v>52.080000000000005</v>
       </c>
-      <c r="Z19" s="83"/>
+      <c r="Z19" s="78"/>
       <c r="AA19" s="26"/>
       <c r="AB19" s="26"/>
-      <c r="AC19" s="82">
+      <c r="AC19" s="76">
         <f>AC18*AB7</f>
         <v>18.015999999999998</v>
       </c>
-      <c r="AD19" s="119"/>
-      <c r="AE19" s="119">
+      <c r="AD19" s="77"/>
+      <c r="AE19" s="77">
         <f t="shared" ref="AE19" si="1">AE18*AD7</f>
         <v>0</v>
       </c>
-      <c r="AF19" s="83"/>
+      <c r="AF19" s="78"/>
     </row>
     <row r="20" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="21" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2860,25 +2861,25 @@
   <sheetData>
     <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="120" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
-      <c r="F2" s="79" t="s">
+      <c r="B2" s="121"/>
+      <c r="C2" s="122"/>
+      <c r="F2" s="123" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
-      <c r="O2" s="80"/>
-      <c r="P2" s="80"/>
-      <c r="Q2" s="81"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
+      <c r="J2" s="124"/>
+      <c r="K2" s="124"/>
+      <c r="L2" s="124"/>
+      <c r="M2" s="124"/>
+      <c r="N2" s="124"/>
+      <c r="O2" s="124"/>
+      <c r="P2" s="124"/>
+      <c r="Q2" s="125"/>
     </row>
     <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="64" t="s">
@@ -3194,11 +3195,11 @@
         <v>4.7097532314923612E-2</v>
       </c>
       <c r="D13" s="24">
-        <f>IF($A13=1,$G$5,IF($A13&gt;1,E13*C13,$G$5))</f>
+        <f>$G$5</f>
         <v>1.9995759382366515E-2</v>
       </c>
       <c r="E13" s="24">
-        <f>IF($A13=1,$G$6,IF($A13&gt;1,$G$6,D13/C13))</f>
+        <f>D13/C13</f>
         <v>0.42456065954076616</v>
       </c>
       <c r="F13" s="24">
@@ -3210,28 +3211,28 @@
         <v>19.700190965374354</v>
       </c>
       <c r="H13" s="24">
-        <f>IF(A13&gt;1,E13*$G$7*$G$4,D13*$G$4)</f>
+        <f>D13*$G$4</f>
         <v>1000</v>
       </c>
       <c r="I13" s="24">
-        <f>1/(1+'Chemestry H2'!$L$7*('Chemestry H2'!$J$4+1)/A13)</f>
-        <v>0.25316455696202528</v>
+        <f>1/(1+'Chemestry CH4'!$L$7*('Chemestry CH4'!$J$4+1)/A13)</f>
+        <v>7.8125E-2</v>
       </c>
       <c r="J13" s="24">
         <f>1-I13</f>
-        <v>0.74683544303797467</v>
+        <v>0.921875</v>
       </c>
       <c r="K13" s="24">
         <f>I13*$P$8+J13*$P$7</f>
-        <v>25.694556962025313</v>
+        <v>27.959218750000002</v>
       </c>
       <c r="L13" s="24">
         <f>($M$6*K13)/($G$8*$M$5) /1000</f>
-        <v>1.0438220608520627</v>
+        <v>1.1358222435425187</v>
       </c>
       <c r="M13" s="24">
         <f>(D13+E13)/(1000*L13*PI()*($P$5/2)^2)</f>
-        <v>1.2296229015808884</v>
+        <v>1.1300249827789264</v>
       </c>
       <c r="N13" s="24">
         <f>M13*L13*$P$5/([1]!PropsSI("V","T",$M$5,"P",$M$6,"Air"))</f>
@@ -3252,11 +3253,11 @@
         <v>5.8871915393654516E-2</v>
       </c>
       <c r="D14" s="24">
-        <f t="shared" ref="D14:D15" si="2">IF($A14=1,$G$5,IF($A14&gt;1,E14*C14,$G$5))</f>
+        <f t="shared" ref="D14:D15" si="2">$G$5</f>
         <v>1.9995759382366515E-2</v>
       </c>
       <c r="E14" s="24">
-        <f t="shared" ref="E14:E15" si="3">IF($A14=1,$G$6,IF($A14&gt;1,$G$6,D14/C14))</f>
+        <f t="shared" ref="E14:E15" si="3">D14/C14</f>
         <v>0.33964852763261294</v>
       </c>
       <c r="F14" s="24">
@@ -3268,7 +3269,7 @@
         <v>15.760152772299481</v>
       </c>
       <c r="H14" s="24">
-        <f t="shared" ref="H14:H15" si="5">IF(A14&gt;1,E14*$G$7*$G$4,D14*$G$4)</f>
+        <f t="shared" ref="H14:H15" si="5">D14*$G$4</f>
         <v>1000</v>
       </c>
       <c r="I14" s="24">
@@ -3311,19 +3312,19 @@
       </c>
       <c r="D15" s="24">
         <f t="shared" si="2"/>
-        <v>2.3994911258839822E-2</v>
+        <v>1.9995759382366515E-2</v>
       </c>
       <c r="E15" s="24">
         <f t="shared" si="3"/>
-        <v>0.33964852763261294</v>
+        <v>0.28304043969384407</v>
       </c>
       <c r="F15" s="24">
         <f t="shared" ref="F15" si="8">D15/($J$7*1000)*1000*60</f>
-        <v>2.0066583912508253</v>
+        <v>1.672215326042354</v>
       </c>
       <c r="G15" s="24">
         <f t="shared" si="4"/>
-        <v>15.760152772299481</v>
+        <v>13.133460643582898</v>
       </c>
       <c r="H15" s="24">
         <f t="shared" si="5"/>
@@ -3347,11 +3348,11 @@
       </c>
       <c r="M15" s="24">
         <f>(D15+E15)/(1000*L15*PI()*($P$5/2)^2)</f>
-        <v>0.93941675294957117</v>
+        <v>0.78284729412464249</v>
       </c>
       <c r="N15" s="24">
         <f>M15*L15*$P$5/([1]!PropsSI("V","T",$M$5,"P",$M$6,"Air"))</f>
-        <v>1189.375950086717</v>
+        <v>991.14662507226376</v>
       </c>
     </row>
   </sheetData>
@@ -3388,32 +3389,32 @@
   <sheetData>
     <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="120" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
-      <c r="F2" s="79" t="s">
+      <c r="B2" s="121"/>
+      <c r="C2" s="122"/>
+      <c r="F2" s="123" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
-      <c r="O2" s="80"/>
-      <c r="P2" s="80"/>
-      <c r="Q2" s="81"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
+      <c r="J2" s="124"/>
+      <c r="K2" s="124"/>
+      <c r="L2" s="124"/>
+      <c r="M2" s="124"/>
+      <c r="N2" s="124"/>
+      <c r="O2" s="124"/>
+      <c r="P2" s="124"/>
+      <c r="Q2" s="125"/>
     </row>
     <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="64" t="s">
         <v>33</v>
       </c>
       <c r="B3" s="65">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="C3" s="66" t="s">
         <v>34</v>
@@ -3501,7 +3502,7 @@
       </c>
       <c r="G5" s="59">
         <f>B3/G4</f>
-        <v>8.3371241884123894E-3</v>
+        <v>2.0842810471030974E-3</v>
       </c>
       <c r="H5" s="60" t="s">
         <v>40</v>
@@ -3543,7 +3544,7 @@
       </c>
       <c r="G6" s="74">
         <f>G5*'Chemestry H2'!B29</f>
-        <v>0.28154336048964068</v>
+        <v>7.038584012241017E-2</v>
       </c>
       <c r="H6" s="60" t="s">
         <v>42</v>
@@ -3722,48 +3723,48 @@
         <v>1.4806110458284368E-2</v>
       </c>
       <c r="D13" s="24">
-        <f>IF($A13=1,$G$5,IF($A13&gt;1,E13*C13,$G$5))</f>
-        <v>8.3371241884123894E-3</v>
+        <f>$G$5</f>
+        <v>2.0842810471030974E-3</v>
       </c>
       <c r="E13" s="24">
-        <f>IF($A13=1,$G$6,IF($A13&gt;1,$G$6,D13/C13))</f>
-        <v>0.56308672097928136</v>
+        <f>D13/C13</f>
+        <v>0.14077168024482034</v>
       </c>
       <c r="F13" s="24">
         <f>D13/($J$7*1000)*1000*60</f>
-        <v>5.5653563181636887</v>
+        <v>1.3913390795409222</v>
       </c>
       <c r="G13" s="24">
         <f>E13/($J$8*1000)*1000*60</f>
-        <v>26.12798827229344</v>
+        <v>6.5319970680733599</v>
       </c>
       <c r="H13" s="24">
         <f>IF(A13&gt;1,E13*$G$7*$G$4,D13*$G$4)</f>
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="I13" s="24">
-        <f>1/(1+'Chemestry CH4'!$L$7*('Chemestry CH4'!$J$4+1)/A13)</f>
-        <v>5.0301810865191143E-2</v>
+        <f>1/(1+'Chemestry H2'!$L$7*('Chemestry H2'!$J$4+1)/A13)</f>
+        <v>0.17482517482517482</v>
       </c>
       <c r="J13" s="24">
         <f>1-I13</f>
-        <v>0.94969818913480886</v>
+        <v>0.82517482517482521</v>
       </c>
       <c r="K13" s="24">
         <f>I13*$P$8+J13*$P$7</f>
-        <v>27.614164989939638</v>
+        <v>24.25776223776224</v>
       </c>
       <c r="L13" s="24">
         <f>($M$6*K13)/($G$8*$M$5) /1000</f>
-        <v>1.1218046939321764</v>
+        <v>0.98545335528075506</v>
       </c>
       <c r="M13" s="24">
         <f>(D13+E13)/(1000*L13*PI()*($P$5/2)^2)</f>
-        <v>40.535099403192014</v>
+        <v>11.535925200273198</v>
       </c>
       <c r="N13" s="24">
         <f>M13*L13*$P$5/([1]!PropsSI("V","T",$M$5,"P",$M$6,"Air"))</f>
-        <v>9812.079517526674</v>
+        <v>2453.019879381668</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -3780,48 +3781,48 @@
         <v>1.7767332549941242E-2</v>
       </c>
       <c r="D14" s="24">
-        <f t="shared" ref="D14:D21" si="2">IF($A14=1,$G$5,IF($A14&gt;1,E14*C14,$G$5))</f>
-        <v>8.3371241884123894E-3</v>
+        <f t="shared" ref="D14:D21" si="2">$G$5</f>
+        <v>2.0842810471030974E-3</v>
       </c>
       <c r="E14" s="24">
-        <f t="shared" ref="E14" si="3">IF($A14=1,$G$6,IF($A14&gt;1,$G$6,D14/C14))</f>
-        <v>0.4692389341494011</v>
+        <f t="shared" ref="E14:E21" si="3">D14/C14</f>
+        <v>0.11730973353735027</v>
       </c>
       <c r="F14" s="24">
         <f t="shared" ref="F14" si="4">D14/($J$7*1000)*1000*60</f>
-        <v>5.5653563181636887</v>
+        <v>1.3913390795409222</v>
       </c>
       <c r="G14" s="24">
         <f t="shared" ref="G14" si="5">E14/($J$8*1000)*1000*60</f>
-        <v>21.773323560244535</v>
+        <v>5.4433308900611337</v>
       </c>
       <c r="H14" s="24">
         <f t="shared" ref="H14" si="6">IF(A14&gt;1,E14*$G$7*$G$4,D14*$G$4)</f>
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="I14" s="24">
-        <f>1/(1+'Chemestry CH4'!$L$7*('Chemestry CH4'!$J$4+1)/A14)</f>
-        <v>5.97609561752988E-2</v>
+        <f>1/(1+'Chemestry H2'!$L$7*('Chemestry H2'!$J$4+1)/A14)</f>
+        <v>0.20270270270270269</v>
       </c>
       <c r="J14" s="24">
         <f t="shared" ref="J14:J21" si="7">1-I14</f>
-        <v>0.94023904382470125</v>
+        <v>0.79729729729729737</v>
       </c>
       <c r="K14" s="24">
         <f>I14*$P$8+J14*$P$7</f>
-        <v>27.359203187250998</v>
+        <v>23.506351351351352</v>
       </c>
       <c r="L14" s="24">
         <f t="shared" ref="L14:L21" si="8">($M$6*K14)/($G$8*$M$5) /1000</f>
-        <v>1.1114470623639674</v>
+        <v>0.95492785288897275</v>
       </c>
       <c r="M14" s="24">
         <f>(D14+E14)/(1000*L14*PI()*($P$5/2)^2)</f>
-        <v>34.193527051635563</v>
+        <v>9.94952002877171</v>
       </c>
       <c r="N14" s="24">
         <f>M14*L14*$P$5/([1]!PropsSI("V","T",$M$5,"P",$M$6,"Air"))</f>
-        <v>8200.5927818822365</v>
+        <v>2050.1481954705591</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.3">
@@ -3839,52 +3840,52 @@
       </c>
       <c r="D15" s="24">
         <f t="shared" si="2"/>
-        <v>8.3371241884123894E-3</v>
+        <v>2.0842810471030974E-3</v>
       </c>
       <c r="E15" s="24">
-        <f t="shared" ref="E15" si="10">IF($A15=1,$G$6,IF($A15&gt;1,$G$6,D15/C15))</f>
-        <v>0.40220480069948666</v>
+        <f t="shared" si="3"/>
+        <v>0.10055120017487167</v>
       </c>
       <c r="F15" s="24">
-        <f t="shared" ref="F15" si="11">D15/($J$7*1000)*1000*60</f>
-        <v>5.5653563181636887</v>
+        <f t="shared" ref="F15" si="10">D15/($J$7*1000)*1000*60</f>
+        <v>1.3913390795409222</v>
       </c>
       <c r="G15" s="24">
-        <f t="shared" ref="G15" si="12">E15/($J$8*1000)*1000*60</f>
-        <v>18.662848765923883</v>
+        <f t="shared" ref="G15" si="11">E15/($J$8*1000)*1000*60</f>
+        <v>4.6657121914809707</v>
       </c>
       <c r="H15" s="24">
-        <f t="shared" ref="H15" si="13">IF(A15&gt;1,E15*$G$7*$G$4,D15*$G$4)</f>
-        <v>1000</v>
+        <f t="shared" ref="H15" si="12">IF(A15&gt;1,E15*$G$7*$G$4,D15*$G$4)</f>
+        <v>250</v>
       </c>
       <c r="I15" s="24">
-        <f>1/(1+'Chemestry CH4'!$L$7*('Chemestry CH4'!$J$4+1)/A15)</f>
-        <v>6.9033530571992102E-2</v>
+        <f>1/(1+'Chemestry H2'!$L$7*('Chemestry H2'!$J$4+1)/A15)</f>
+        <v>0.22875816993464049</v>
       </c>
       <c r="J15" s="24">
         <f t="shared" si="7"/>
-        <v>0.93096646942800787</v>
+        <v>0.77124183006535951</v>
       </c>
       <c r="K15" s="24">
         <f>I15*$P$8+J15*$P$7</f>
-        <v>27.109270216962525</v>
+        <v>22.804052287581698</v>
       </c>
       <c r="L15" s="24">
         <f t="shared" si="8"/>
-        <v>1.1012937233316207</v>
+        <v>0.92639748137247035</v>
       </c>
       <c r="M15" s="24">
         <f>(D15+E15)/(1000*L15*PI()*($P$5/2)^2)</f>
-        <v>29.665009119776705</v>
+        <v>8.8163798485787357</v>
       </c>
       <c r="N15" s="24">
         <f>M15*L15*$P$5/([1]!PropsSI("V","T",$M$5,"P",$M$6,"Air"))</f>
-        <v>7049.530827850499</v>
+        <v>1762.3827069626245</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="72">
-        <f t="shared" ref="A16:A21" si="14">A15+0.1</f>
+        <f t="shared" ref="A16:A21" si="13">A15+0.1</f>
         <v>0.79999999999999993</v>
       </c>
       <c r="B16" s="24" t="str">
@@ -3892,57 +3893,57 @@
         <v>Fuel</v>
       </c>
       <c r="C16" s="24">
-        <f t="shared" ref="C16:C21" si="15">A16*$G$7</f>
+        <f t="shared" ref="C16:C21" si="14">A16*$G$7</f>
         <v>2.3689776733254987E-2</v>
       </c>
       <c r="D16" s="24">
         <f t="shared" si="2"/>
-        <v>8.3371241884123894E-3</v>
+        <v>2.0842810471030974E-3</v>
       </c>
       <c r="E16" s="24">
-        <f t="shared" ref="E16:E21" si="16">IF($A16=1,$G$6,IF($A16&gt;1,$G$6,D16/C16))</f>
-        <v>0.35192920061205085</v>
+        <f t="shared" si="3"/>
+        <v>8.7982300153012713E-2</v>
       </c>
       <c r="F16" s="24">
-        <f t="shared" ref="F16:F21" si="17">D16/($J$7*1000)*1000*60</f>
-        <v>5.5653563181636887</v>
+        <f t="shared" ref="F16:F21" si="15">D16/($J$7*1000)*1000*60</f>
+        <v>1.3913390795409222</v>
       </c>
       <c r="G16" s="24">
-        <f t="shared" ref="G16:G21" si="18">E16/($J$8*1000)*1000*60</f>
-        <v>16.329992670183405</v>
+        <f t="shared" ref="G16:G21" si="16">E16/($J$8*1000)*1000*60</f>
+        <v>4.0824981675458512</v>
       </c>
       <c r="H16" s="24">
-        <f t="shared" ref="H16:H21" si="19">IF(A16&gt;1,E16*$G$7*$G$4,D16*$G$4)</f>
-        <v>1000</v>
+        <f t="shared" ref="H16:H21" si="17">IF(A16&gt;1,E16*$G$7*$G$4,D16*$G$4)</f>
+        <v>250</v>
       </c>
       <c r="I16" s="24">
-        <f>1/(1+'Chemestry CH4'!$L$7*('Chemestry CH4'!$J$4+1)/A16)</f>
-        <v>7.8124999999999986E-2</v>
+        <f>1/(1+'Chemestry H2'!$L$7*('Chemestry H2'!$J$4+1)/A16)</f>
+        <v>0.25316455696202528</v>
       </c>
       <c r="J16" s="24">
         <f t="shared" si="7"/>
-        <v>0.921875</v>
+        <v>0.74683544303797467</v>
       </c>
       <c r="K16" s="24">
-        <f t="shared" ref="K16:K21" si="20">I16*$P$8+J16*$P$7</f>
-        <v>26.864218749999999</v>
+        <f t="shared" ref="K16:K21" si="18">I16*$P$8+J16*$P$7</f>
+        <v>22.146202531645567</v>
       </c>
       <c r="L16" s="24">
         <f t="shared" si="8"/>
-        <v>1.0913386917022492</v>
+        <v>0.89967282957220251</v>
       </c>
       <c r="M16" s="24">
-        <f t="shared" ref="M16:M21" si="21">(D16+E16)/(1000*L16*PI()*($P$5/2)^2)</f>
-        <v>26.269647936750523</v>
+        <f t="shared" ref="M16:M21" si="19">(D16+E16)/(1000*L16*PI()*($P$5/2)^2)</f>
+        <v>7.9665302397773461</v>
       </c>
       <c r="N16" s="24">
         <f>M16*L16*$P$5/([1]!PropsSI("V","T",$M$5,"P",$M$6,"Air"))</f>
-        <v>6186.2343623266961</v>
+        <v>1546.5585905816743</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="72">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.89999999999999991</v>
       </c>
       <c r="B17" s="24" t="str">
@@ -3950,28 +3951,28 @@
         <v>Fuel</v>
       </c>
       <c r="C17" s="24">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>2.665099882491186E-2</v>
       </c>
       <c r="D17" s="24">
         <f t="shared" si="2"/>
-        <v>8.3371241884123894E-3</v>
+        <v>2.0842810471030974E-3</v>
       </c>
       <c r="E17" s="24">
+        <f t="shared" si="3"/>
+        <v>7.8206489024900197E-2</v>
+      </c>
+      <c r="F17" s="24">
+        <f t="shared" si="15"/>
+        <v>1.3913390795409222</v>
+      </c>
+      <c r="G17" s="24">
         <f t="shared" si="16"/>
-        <v>0.31282595609960079</v>
-      </c>
-      <c r="F17" s="24">
+        <v>3.6288872600407558</v>
+      </c>
+      <c r="H17" s="24">
         <f t="shared" si="17"/>
-        <v>5.5653563181636887</v>
-      </c>
-      <c r="G17" s="24">
-        <f t="shared" si="18"/>
-        <v>14.515549040163023</v>
-      </c>
-      <c r="H17" s="24">
-        <f t="shared" si="19"/>
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="I17" s="24">
         <f>1/(1+'Chemestry CH4'!$L$7*('Chemestry CH4'!$J$4+1)/A17)</f>
@@ -3982,7 +3983,7 @@
         <v>0.91295938104448748</v>
       </c>
       <c r="K17" s="24">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>26.623907156673113</v>
       </c>
       <c r="L17" s="24">
@@ -3990,17 +3991,17 @@
         <v>1.081576213876154</v>
       </c>
       <c r="M17" s="24">
-        <f t="shared" si="21"/>
-        <v>23.629722580192322</v>
+        <f t="shared" si="19"/>
+        <v>5.9074306450480805</v>
       </c>
       <c r="N17" s="24">
         <f>M17*L17*$P$5/([1]!PropsSI("V","T",$M$5,"P",$M$6,"Air"))</f>
-        <v>5514.7815558081829</v>
+        <v>1378.6953889520457</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="72">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.99999999999999989</v>
       </c>
       <c r="B18" s="24" t="str">
@@ -4008,28 +4009,28 @@
         <v>Stoc</v>
       </c>
       <c r="C18" s="24">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>2.9612220916568732E-2</v>
       </c>
       <c r="D18" s="24">
         <f t="shared" si="2"/>
-        <v>8.3371241884123894E-3</v>
+        <v>2.0842810471030974E-3</v>
       </c>
       <c r="E18" s="24">
+        <f t="shared" si="3"/>
+        <v>7.0385840122410184E-2</v>
+      </c>
+      <c r="F18" s="24">
+        <f t="shared" si="15"/>
+        <v>1.3913390795409222</v>
+      </c>
+      <c r="G18" s="24">
         <f t="shared" si="16"/>
-        <v>0.28154336048964068</v>
-      </c>
-      <c r="F18" s="24">
+        <v>3.2659985340366808</v>
+      </c>
+      <c r="H18" s="24">
         <f t="shared" si="17"/>
-        <v>5.5653563181636887</v>
-      </c>
-      <c r="G18" s="24">
-        <f t="shared" si="18"/>
-        <v>13.06399413614672</v>
-      </c>
-      <c r="H18" s="24">
-        <f t="shared" si="19"/>
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="I18" s="24">
         <f>1/(1+'Chemestry CH4'!$L$7*('Chemestry CH4'!$J$4+1)/A18)</f>
@@ -4040,7 +4041,7 @@
         <v>0.90421455938697326</v>
       </c>
       <c r="K18" s="24">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>26.388199233716477</v>
       </c>
       <c r="L18" s="24">
@@ -4048,17 +4049,17 @@
         <v>1.0720007566980685</v>
       </c>
       <c r="M18" s="24">
-        <f t="shared" si="21"/>
-        <v>21.518600501968145</v>
+        <f t="shared" si="19"/>
+        <v>5.379650125492037</v>
       </c>
       <c r="N18" s="24">
         <f>M18*L18*$P$5/([1]!PropsSI("V","T",$M$5,"P",$M$6,"Air"))</f>
-        <v>4977.6193105933708</v>
+        <v>1244.4048276483427</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="72">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0999999999999999</v>
       </c>
       <c r="B19" s="24" t="str">
@@ -4066,28 +4067,28 @@
         <v>air</v>
       </c>
       <c r="C19" s="24">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>3.2573443008225608E-2</v>
       </c>
       <c r="D19" s="24">
         <f t="shared" si="2"/>
-        <v>9.1708366072536275E-3</v>
+        <v>2.0842810471030974E-3</v>
       </c>
       <c r="E19" s="24">
+        <f t="shared" si="3"/>
+        <v>6.3987127384009246E-2</v>
+      </c>
+      <c r="F19" s="24">
+        <f t="shared" si="15"/>
+        <v>1.3913390795409222</v>
+      </c>
+      <c r="G19" s="24">
         <f t="shared" si="16"/>
-        <v>0.28154336048964068</v>
-      </c>
-      <c r="F19" s="24">
+        <v>2.969089576396982</v>
+      </c>
+      <c r="H19" s="24">
         <f t="shared" si="17"/>
-        <v>6.1218919499800561</v>
-      </c>
-      <c r="G19" s="24">
-        <f t="shared" si="18"/>
-        <v>13.06399413614672</v>
-      </c>
-      <c r="H19" s="24">
-        <f t="shared" si="19"/>
-        <v>1000</v>
+        <v>227.27272727272728</v>
       </c>
       <c r="I19" s="24">
         <f>1/(1+'Chemestry CH4'!$L$7*('Chemestry CH4'!$J$4+1)/A19)</f>
@@ -4098,7 +4099,7 @@
         <v>0.89563567362428842</v>
       </c>
       <c r="K19" s="24">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>26.15696394686907</v>
       </c>
       <c r="L19" s="24">
@@ -4106,17 +4107,17 @@
         <v>1.0626069969996426</v>
       </c>
       <c r="M19" s="24">
-        <f t="shared" si="21"/>
-        <v>21.771267093857571</v>
+        <f t="shared" si="19"/>
+        <v>4.9480152486039932</v>
       </c>
       <c r="N19" s="24">
         <f>M19*L19*$P$5/([1]!PropsSI("V","T",$M$5,"P",$M$6,"Air"))</f>
-        <v>4991.9352209593771</v>
+        <v>1134.5307320362219</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="72">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.2</v>
       </c>
       <c r="B20" s="24" t="str">
@@ -4124,28 +4125,28 @@
         <v>air</v>
       </c>
       <c r="C20" s="24">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>3.5534665099882484E-2</v>
       </c>
       <c r="D20" s="24">
         <f t="shared" si="2"/>
-        <v>1.0004549026094867E-2</v>
+        <v>2.0842810471030974E-3</v>
       </c>
       <c r="E20" s="24">
+        <f t="shared" si="3"/>
+        <v>5.8654866768675137E-2</v>
+      </c>
+      <c r="F20" s="24">
+        <f t="shared" si="15"/>
+        <v>1.3913390795409222</v>
+      </c>
+      <c r="G20" s="24">
         <f t="shared" si="16"/>
-        <v>0.28154336048964068</v>
-      </c>
-      <c r="F20" s="24">
+        <v>2.7216654450305668</v>
+      </c>
+      <c r="H20" s="24">
         <f t="shared" si="17"/>
-        <v>6.6784275817964271</v>
-      </c>
-      <c r="G20" s="24">
-        <f t="shared" si="18"/>
-        <v>13.06399413614672</v>
-      </c>
-      <c r="H20" s="24">
-        <f t="shared" si="19"/>
-        <v>1000</v>
+        <v>208.33333333333331</v>
       </c>
       <c r="I20" s="24">
         <f>1/(1+'Chemestry CH4'!$L$7*('Chemestry CH4'!$J$4+1)/A20)</f>
@@ -4156,7 +4157,7 @@
         <v>0.88721804511278202</v>
       </c>
       <c r="K20" s="24">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>25.930075187969926</v>
       </c>
       <c r="L20" s="24">
@@ -4164,17 +4165,17 @@
         <v>1.0533898117316385</v>
       </c>
       <c r="M20" s="24">
-        <f t="shared" si="21"/>
-        <v>22.024748308159612</v>
+        <f t="shared" si="19"/>
+        <v>4.5884892308665854</v>
       </c>
       <c r="N20" s="24">
         <f>M20*L20*$P$5/([1]!PropsSI("V","T",$M$5,"P",$M$6,"Air"))</f>
-        <v>5006.2511313253854</v>
+        <v>1042.9689856927885</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="72">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.3</v>
       </c>
       <c r="B21" s="24" t="str">
@@ -4182,28 +4183,28 @@
         <v>air</v>
       </c>
       <c r="C21" s="24">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>3.849588719153936E-2</v>
       </c>
       <c r="D21" s="24">
         <f t="shared" si="2"/>
-        <v>1.0838261444936107E-2</v>
+        <v>2.0842810471030974E-3</v>
       </c>
       <c r="E21" s="24">
+        <f t="shared" si="3"/>
+        <v>5.4142953940315507E-2</v>
+      </c>
+      <c r="F21" s="24">
+        <f t="shared" si="15"/>
+        <v>1.3913390795409222</v>
+      </c>
+      <c r="G21" s="24">
         <f t="shared" si="16"/>
-        <v>0.28154336048964068</v>
-      </c>
-      <c r="F21" s="24">
+        <v>2.5123065646435996</v>
+      </c>
+      <c r="H21" s="24">
         <f t="shared" si="17"/>
-        <v>7.2349632136127964</v>
-      </c>
-      <c r="G21" s="24">
-        <f t="shared" si="18"/>
-        <v>13.06399413614672</v>
-      </c>
-      <c r="H21" s="24">
-        <f t="shared" si="19"/>
-        <v>1000</v>
+        <v>192.30769230769226</v>
       </c>
       <c r="I21" s="24">
         <f>1/(1+'Chemestry CH4'!$L$7*('Chemestry CH4'!$J$4+1)/A21)</f>
@@ -4214,7 +4215,7 @@
         <v>0.87895716945996272</v>
       </c>
       <c r="K21" s="24">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>25.707411545623835</v>
       </c>
       <c r="L21" s="24">
@@ -4222,12 +4223,12 @@
         <v>1.044344268647396</v>
       </c>
       <c r="M21" s="24">
-        <f t="shared" si="21"/>
-        <v>22.279042360419648</v>
+        <f t="shared" si="19"/>
+        <v>4.2844312231576245</v>
       </c>
       <c r="N21" s="24">
         <f>M21*L21*$P$5/([1]!PropsSI("V","T",$M$5,"P",$M$6,"Air"))</f>
-        <v>5020.5670416913908</v>
+        <v>965.49366186372902</v>
       </c>
     </row>
   </sheetData>
